--- a/Data/Importfiles-CD.xlsx
+++ b/Data/Importfiles-CD.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clinicalmicrobiomics-my.sharepoint.com/personal/dama_cmbio_io/Documents/Documents/R scripts/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clinicalmicrobiomics.sharepoint.com/sites/Teamwebsted/MSOmics Team Folder/Daniel/PhD/Manuscript/Github/Matrix-Effects-and-Interferences/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_0EE4D886D53525D15102F9F5A679E0C47DB3CD20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3D99916-0E5B-4495-A58B-16EB27DCD889}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_0EE4D886D53525D15102F9F5A679E0C47DB3CD20" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A73AEC39-D5FB-46F9-BDA1-8D608126EE84}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InputFiles" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">InputFiles!$A$1:$H$55</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -944,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H55"/>
@@ -985,7 +988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1011,7 +1014,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -1063,7 +1066,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -1089,7 +1092,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1115,7 +1118,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
@@ -1141,7 +1144,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1167,7 +1170,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
@@ -1193,7 +1196,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1219,7 +1222,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -1245,7 +1248,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -1349,7 +1352,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>56</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>59</v>
       </c>
@@ -1401,7 +1404,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>62</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>65</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>77</v>
       </c>
@@ -1557,7 +1560,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>80</v>
       </c>
@@ -1583,7 +1586,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>83</v>
       </c>
@@ -1609,7 +1612,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>86</v>
       </c>
@@ -1713,7 +1716,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
         <v>98</v>
       </c>
@@ -1739,7 +1742,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>101</v>
       </c>
@@ -1765,7 +1768,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>104</v>
       </c>
@@ -1791,7 +1794,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>107</v>
       </c>
@@ -1895,7 +1898,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>119</v>
       </c>
@@ -1921,7 +1924,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>122</v>
       </c>
@@ -1947,7 +1950,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>125</v>
       </c>
@@ -1973,7 +1976,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>128</v>
       </c>
@@ -2077,7 +2080,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2" t="s">
         <v>140</v>
       </c>
@@ -2181,7 +2184,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
         <v>152</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2" t="s">
         <v>155</v>
       </c>
@@ -2233,7 +2236,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2" t="s">
         <v>158</v>
       </c>
@@ -2259,7 +2262,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2" t="s">
         <v>161</v>
       </c>
@@ -2285,7 +2288,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2" t="s">
         <v>164</v>
       </c>
@@ -2311,7 +2314,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2" t="s">
         <v>167</v>
       </c>
@@ -2337,7 +2340,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -2363,7 +2366,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2" t="s">
         <v>173</v>
       </c>
@@ -2390,13 +2393,46 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H55" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-014-22x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-015-22x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-016-22x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-021-08x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-022-08x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-023-08x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-028-04x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-029-04x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-030-04x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-035-NoWash-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-036-NoWash-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-037-NoWash-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-042-PPT-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-043-PPT-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-044-PPT-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-046-22x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-047-22x-NIST.raw"/>
+        <filter val="S:\raw data Q Exactive\@Experiments\DP00026-PhD Project\Exp7-241008\241008-Exp-PAN-1-048-22x-NIST.raw"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070A374496BE7274781128F0D831E72DD" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d7cc277b9cf2e7a60190beb1db4661cc">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fff87b9b-1ac5-4ef1-8252-e3ce3ef06456" xmlns:ns3="513e5f18-c1fe-4153-a26e-6964a418bd27" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bfa282b62c6add100787f472353d6258" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070A374496BE7274781128F0D831E72DD" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7a4ad6a196041dd3394f17e1f77d0180">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fff87b9b-1ac5-4ef1-8252-e3ce3ef06456" xmlns:ns3="513e5f18-c1fe-4153-a26e-6964a418bd27" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5020376e02439b7ed831ffcd2c682bcd" ns2:_="" ns3:_="">
     <xsd:import namespace="fff87b9b-1ac5-4ef1-8252-e3ce3ef06456"/>
     <xsd:import namespace="513e5f18-c1fe-4153-a26e-6964a418bd27"/>
     <xsd:element name="properties">
@@ -2659,15 +2695,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2685,13 +2712,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86A34111-5195-463D-9EC4-B31808EFCC1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E41395E-E61B-4522-A8DF-A4062D5F027B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E41395E-E61B-4522-A8DF-A4062D5F027B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9C540AC-DD45-4708-A692-BF37C651C63A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93558842-451C-4E78-BFFD-1E7AF8D3E880}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93558842-451C-4E78-BFFD-1E7AF8D3E880}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="fff87b9b-1ac5-4ef1-8252-e3ce3ef06456"/>
+    <ds:schemaRef ds:uri="513e5f18-c1fe-4153-a26e-6964a418bd27"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>